--- a/dados/excel/resumo_secretaria.xlsx
+++ b/dados/excel/resumo_secretaria.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>﻿secretaria</t>
+          <t>secretaria</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -836,7 +836,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -849,7 +849,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>﻿secretaria</t>
+          <t>secretaria</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
@@ -900,28 +900,28 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>2678559783.94</v>
+        <v>2741216255.29</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>1693107361.44</v>
+        <v>1734185313.11</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>489718</v>
+        <v>498585</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>17451</v>
+        <v>17796</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>47831424.71321429</v>
+        <v>48091513.25</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>45.74</v>
+        <v>45.79</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -931,28 +931,28 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1702152685.65</v>
+        <v>1737125661.76</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>1119958539.78</v>
+        <v>1143142931.92</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>182464</v>
+        <v>185700</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>3963</v>
+        <v>3977</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3" s="13" t="n">
-        <v>30395583.67232143</v>
+        <v>30475888.8</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>29.06</v>
+        <v>29.02</v>
       </c>
       <c r="I3" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -962,28 +962,28 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>275530796.97</v>
+        <v>281796826.63</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>171771662.33</v>
+        <v>175956866.41</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>28006</v>
+        <v>28617</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>803</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>4920192.803035715</v>
+        <v>4943803.98</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
@@ -993,28 +993,28 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>134268631.67</v>
+        <v>137257947.56</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>89958310.22</v>
+        <v>91989298.13</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>18549</v>
+        <v>18886</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>2397654.136964285</v>
+        <v>2408034.17</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>2.29</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -1024,28 +1024,28 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>126977557.7</v>
+        <v>129599355.27</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>81615417.27</v>
+        <v>83317954.14</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>8939</v>
+        <v>9086</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>2267456.3875</v>
+        <v>2273672.9</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -1055,28 +1055,28 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>111789935.25</v>
+        <v>113407036.47</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>74372448.87</v>
+        <v>75523385.41</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>16227</v>
+        <v>16393</v>
       </c>
       <c r="E7" s="14" t="n">
         <v>585</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1996248.84375</v>
+        <v>1989597.13</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -1086,28 +1086,28 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>109752123.28</v>
+        <v>112209525.04</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>71805409.37</v>
+        <v>73438818.20999999</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>12832</v>
+        <v>13011</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>304</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>1959859.344285714</v>
+        <v>1968588.16</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>1.87</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -1117,28 +1117,28 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>78948241.51000001</v>
+        <v>80789672.72</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>52607270.45</v>
+        <v>53848105.68</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>10345</v>
+        <v>10540</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>1794278.216136364</v>
+        <v>1795326.06</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>1.35</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -1148,28 +1148,28 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>76779939.69</v>
+        <v>78476095.31</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>52875842.28</v>
+        <v>54040501.58</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>7547</v>
+        <v>7682</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>1371070.351607143</v>
+        <v>1376773.6</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>1.31</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -1179,28 +1179,28 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>76637568.31999999</v>
+        <v>78250977.20999999</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>51066095.36</v>
+        <v>52202594.83</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>9931</v>
+        <v>10095</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1368528.005714286</v>
+        <v>1372824.16</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>1.31</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
@@ -1210,28 +1210,28 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>66273277.01</v>
+        <v>68086222.88</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>44201602.43</v>
+        <v>45443269.84</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>6712</v>
+        <v>6891</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>1183451.375178571</v>
+        <v>1194495.14</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -1241,28 +1241,28 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>60778899.47</v>
+        <v>62166911.17</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>40848218.93</v>
+        <v>41767347.28</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>7788</v>
+        <v>7953</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>1085337.490535714</v>
+        <v>1090647.56</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>1.04</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
@@ -1272,28 +1272,28 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>60308422.97</v>
+        <v>61630502.57</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>40872155.58</v>
+        <v>41780193.1</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>8351</v>
+        <v>8490</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>1076936.124464286</v>
+        <v>1081236.89</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>1.03</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -1303,28 +1303,28 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>54438312.8</v>
+        <v>55512090.86</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>28013198.44</v>
+        <v>28564187.17</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>11288</v>
+        <v>11464</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>297</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>1237234.381818182</v>
+        <v>1233602.02</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>0.93</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
@@ -1334,28 +1334,28 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>50182813.56</v>
+        <v>51348481.87</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>32119281.47</v>
+        <v>32936340.95</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>5873</v>
+        <v>5978</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>896121.6707142858</v>
+        <v>900850.5600000001</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>0.86</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
@@ -1365,28 +1365,28 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>28853770.39</v>
+        <v>29075458.45</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>18150482.06</v>
+        <v>18302798.52</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>4247</v>
+        <v>4267</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>251</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>515245.8998214286</v>
+        <v>510095.76</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>0.49</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
@@ -1396,28 +1396,28 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>27859834.98</v>
+        <v>28448076.15</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>18684772.78</v>
+        <v>19092732.32</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>4631</v>
+        <v>4711</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>497497.0532142857</v>
+        <v>499089.06</v>
       </c>
       <c r="H18" s="11" t="n">
         <v>0.48</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -1427,28 +1427,28 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>21471305.11</v>
+        <v>21946438.21</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>14813491.61</v>
+        <v>15153313.05</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>2633</v>
+        <v>2677</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>93</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>383416.1626785714</v>
+        <v>385025.23</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>0.37</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -1458,28 +1458,28 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>19764352.81</v>
+        <v>20165691.06</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>14043943.45</v>
+        <v>14334083.71</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>2086</v>
+        <v>2122</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>352934.8716071428</v>
+        <v>353784.05</v>
       </c>
       <c r="H20" s="11" t="n">
         <v>0.34</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
@@ -1489,28 +1489,28 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>19433905.54</v>
+        <v>20031357.22</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>12593492.88</v>
+        <v>12989894.75</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>2321</v>
+        <v>2396</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>347034.0275</v>
+        <v>351427.32</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>0.33</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
@@ -1532,13 +1532,13 @@
         <v>228</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>1301670.164166667</v>
+        <v>1301670.16</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>12</v>
@@ -1551,28 +1551,28 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>13372068.18</v>
+        <v>13537592.39</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>7841827.92</v>
+        <v>7952134.77</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>2522</v>
+        <v>2532</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>334301.7045</v>
+        <v>330185.18</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>0.23</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24">
@@ -1582,28 +1582,28 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>11842845.19</v>
+        <v>12173947.45</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>7772571.85</v>
+        <v>7983662.06</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>1770</v>
+        <v>1807</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>370088.9121875</v>
+        <v>368907.5</v>
       </c>
       <c r="H24" s="11" t="n">
         <v>0.2</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
@@ -1613,28 +1613,28 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>11078063.81</v>
+        <v>11778468.24</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>7767350.58</v>
+        <v>8282961.84</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>1191</v>
+        <v>1253</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>583055.99</v>
+        <v>588923.41</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -1644,28 +1644,28 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>9324854.25</v>
+        <v>9499670.880000001</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>6454554.56</v>
+        <v>6586631.17</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>166515.2544642857</v>
+        <v>166660.89</v>
       </c>
       <c r="H26" s="11" t="n">
         <v>0.16</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
@@ -1675,28 +1675,28 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>4878843.77</v>
+        <v>5193835.27</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>3261331.29</v>
+        <v>3479700.85</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>517</v>
+        <v>551</v>
       </c>
       <c r="E27" s="14" t="n">
         <v>42</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>256781.2510526316</v>
+        <v>259691.76</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -1706,28 +1706,28 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>3614991.77</v>
+        <v>3792151.5</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>2453925.54</v>
+        <v>2579825.92</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="E28" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>56</v>
-      </c>
       <c r="G28" s="9" t="n">
-        <v>190262.7247368421</v>
+        <v>189607.58</v>
       </c>
       <c r="H28" s="11" t="n">
         <v>0.06</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1737,28 +1737,28 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>3105970.29</v>
+        <v>3268821.38</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>2200251.58</v>
+        <v>2318268.55</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="E29" s="14" t="n">
         <v>30</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>163472.1205263158</v>
+        <v>163441.07</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>0.05</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -1768,28 +1768,28 @@
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>3056665.86</v>
+        <v>3222610.75</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>2184144.06</v>
+        <v>2300940.44</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>19</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>152833.293</v>
+        <v>153457.65</v>
       </c>
       <c r="H30" s="11" t="n">
         <v>0.05</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1808,7 +1808,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -1821,7 +1821,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>﻿secretaria</t>
+          <t>secretaria</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
@@ -1872,28 +1872,28 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>2678559783.94</v>
+        <v>2741216255.29</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>1693107361.44</v>
+        <v>1734185313.11</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>489718</v>
+        <v>498585</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>17451</v>
+        <v>17796</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>47831424.71321429</v>
+        <v>48091513.25</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>45.74</v>
+        <v>45.79</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -1903,28 +1903,28 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1702152685.65</v>
+        <v>1737125661.76</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>1119958539.78</v>
+        <v>1143142931.92</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>182464</v>
+        <v>185700</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>3963</v>
+        <v>3977</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3" s="13" t="n">
-        <v>30395583.67232143</v>
+        <v>30475888.8</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>29.06</v>
+        <v>29.02</v>
       </c>
       <c r="I3" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -1934,28 +1934,28 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>275530796.97</v>
+        <v>281796826.63</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>171771662.33</v>
+        <v>175956866.41</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>28006</v>
+        <v>28617</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>803</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>4920192.803035715</v>
+        <v>4943803.98</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
@@ -1965,28 +1965,28 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>134268631.67</v>
+        <v>137257947.56</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>89958310.22</v>
+        <v>91989298.13</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>18549</v>
+        <v>18886</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>2397654.136964285</v>
+        <v>2408034.17</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>2.29</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -1996,28 +1996,28 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>126977557.7</v>
+        <v>129599355.27</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>81615417.27</v>
+        <v>83317954.14</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>8939</v>
+        <v>9086</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>2267456.3875</v>
+        <v>2273672.9</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -2027,28 +2027,28 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>111789935.25</v>
+        <v>113407036.47</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>74372448.87</v>
+        <v>75523385.41</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>16227</v>
+        <v>16393</v>
       </c>
       <c r="E7" s="14" t="n">
         <v>585</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1996248.84375</v>
+        <v>1989597.13</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -2058,28 +2058,28 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>109752123.28</v>
+        <v>112209525.04</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>71805409.37</v>
+        <v>73438818.20999999</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>12832</v>
+        <v>13011</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>304</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>1959859.344285714</v>
+        <v>1968588.16</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>1.87</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -2089,28 +2089,28 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>78948241.51000001</v>
+        <v>80789672.72</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>52607270.45</v>
+        <v>53848105.68</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>10345</v>
+        <v>10540</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>1794278.216136364</v>
+        <v>1795326.06</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>1.35</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -2120,28 +2120,28 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>76779939.69</v>
+        <v>78476095.31</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>52875842.28</v>
+        <v>54040501.58</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>7547</v>
+        <v>7682</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>1371070.351607143</v>
+        <v>1376773.6</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>1.31</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -2151,28 +2151,28 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>76637568.31999999</v>
+        <v>78250977.20999999</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>51066095.36</v>
+        <v>52202594.83</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>9931</v>
+        <v>10095</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1368528.005714286</v>
+        <v>1372824.16</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>1.31</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
@@ -2182,28 +2182,28 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>66273277.01</v>
+        <v>68086222.88</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>44201602.43</v>
+        <v>45443269.84</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>6712</v>
+        <v>6891</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>1183451.375178571</v>
+        <v>1194495.14</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -2213,28 +2213,28 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>60778899.47</v>
+        <v>62166911.17</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>40848218.93</v>
+        <v>41767347.28</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>7788</v>
+        <v>7953</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>1085337.490535714</v>
+        <v>1090647.56</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>1.04</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>60308422.97</v>
+        <v>61630502.57</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>40872155.58</v>
+        <v>41780193.1</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>8351</v>
+        <v>8490</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>1076936.124464286</v>
+        <v>1081236.89</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>1.03</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2275,28 +2275,28 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>54438312.8</v>
+        <v>55512090.86</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>28013198.44</v>
+        <v>28564187.17</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>11288</v>
+        <v>11464</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>297</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>1237234.381818182</v>
+        <v>1233602.02</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>0.93</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
@@ -2306,28 +2306,28 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>50182813.56</v>
+        <v>51348481.87</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>32119281.47</v>
+        <v>32936340.95</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>5873</v>
+        <v>5978</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>896121.6707142858</v>
+        <v>900850.5600000001</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>0.86</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
@@ -2337,28 +2337,28 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>28853770.39</v>
+        <v>29075458.45</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>18150482.06</v>
+        <v>18302798.52</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>4247</v>
+        <v>4267</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>251</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>515245.8998214286</v>
+        <v>510095.76</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>0.49</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
@@ -2368,28 +2368,28 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>27859834.98</v>
+        <v>28448076.15</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>18684772.78</v>
+        <v>19092732.32</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>4631</v>
+        <v>4711</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>497497.0532142857</v>
+        <v>499089.06</v>
       </c>
       <c r="H18" s="11" t="n">
         <v>0.48</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -2399,28 +2399,28 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>21471305.11</v>
+        <v>21946438.21</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>14813491.61</v>
+        <v>15153313.05</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>2633</v>
+        <v>2677</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>93</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>383416.1626785714</v>
+        <v>385025.23</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>0.37</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -2430,28 +2430,28 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>19764352.81</v>
+        <v>20165691.06</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>14043943.45</v>
+        <v>14334083.71</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>2086</v>
+        <v>2122</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>352934.8716071428</v>
+        <v>353784.05</v>
       </c>
       <c r="H20" s="11" t="n">
         <v>0.34</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
@@ -2461,28 +2461,28 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>19433905.54</v>
+        <v>20031357.22</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>12593492.88</v>
+        <v>12989894.75</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>2321</v>
+        <v>2396</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>347034.0275</v>
+        <v>351427.32</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>0.33</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
@@ -2504,13 +2504,13 @@
         <v>228</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>1301670.164166667</v>
+        <v>1301670.16</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>12</v>
@@ -2523,28 +2523,28 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>13372068.18</v>
+        <v>13537592.39</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>7841827.92</v>
+        <v>7952134.77</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>2522</v>
+        <v>2532</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>334301.7045</v>
+        <v>330185.18</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>0.23</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24">
@@ -2554,28 +2554,28 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>11842845.19</v>
+        <v>12173947.45</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>7772571.85</v>
+        <v>7983662.06</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>1770</v>
+        <v>1807</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>370088.9121875</v>
+        <v>368907.5</v>
       </c>
       <c r="H24" s="11" t="n">
         <v>0.2</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
@@ -2585,28 +2585,28 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>11078063.81</v>
+        <v>11778468.24</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>7767350.58</v>
+        <v>8282961.84</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>1191</v>
+        <v>1253</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>583055.99</v>
+        <v>588923.41</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -2616,28 +2616,28 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>9324854.25</v>
+        <v>9499670.880000001</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>6454554.56</v>
+        <v>6586631.17</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>166515.2544642857</v>
+        <v>166660.89</v>
       </c>
       <c r="H26" s="11" t="n">
         <v>0.16</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
@@ -2647,28 +2647,28 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>4878843.77</v>
+        <v>5193835.27</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>3261331.29</v>
+        <v>3479700.85</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>517</v>
+        <v>551</v>
       </c>
       <c r="E27" s="14" t="n">
         <v>42</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>256781.2510526316</v>
+        <v>259691.76</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -2678,28 +2678,28 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>3614991.77</v>
+        <v>3792151.5</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>2453925.54</v>
+        <v>2579825.92</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="E28" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>56</v>
-      </c>
       <c r="G28" s="9" t="n">
-        <v>190262.7247368421</v>
+        <v>189607.58</v>
       </c>
       <c r="H28" s="11" t="n">
         <v>0.06</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -2709,28 +2709,28 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>3105970.29</v>
+        <v>3268821.38</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>2200251.58</v>
+        <v>2318268.55</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="E29" s="14" t="n">
         <v>30</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>163472.1205263158</v>
+        <v>163441.07</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>0.05</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -2740,28 +2740,28 @@
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>3056665.86</v>
+        <v>3222610.75</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>2184144.06</v>
+        <v>2300940.44</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>19</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>152833.293</v>
+        <v>153457.65</v>
       </c>
       <c r="H30" s="11" t="n">
         <v>0.05</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
